--- a/02_Zero_Shot/outputs/Embedding/XLNet-base-cased/RESULT_f-droid_xlnet-base-cased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/XLNet-base-cased/RESULT_f-droid_xlnet-base-cased_zeroshot.xlsx
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3047426847630459</v>
+        <v>0.3047426847630458</v>
       </c>
     </row>
     <row r="4">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.982535405999442</v>
+        <v>49.4204069740008</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003161751286870624</v>
+        <v>0.01739542660119704</v>
       </c>
     </row>
   </sheetData>
